--- a/uploads/CONTABILITA Green Enerbras One SCSp.xlsx
+++ b/uploads/CONTABILITA Green Enerbras One SCSp.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Edoardo\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Edoardo\.gemini\antigravity\scratch\GREEN_ENERBRAS\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7C391C1-DF66-43DB-845B-9B8779FFA260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEDB55D8-9F74-4BA2-BC55-A676A7F9BF51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Compte Banque" sheetId="3" r:id="rId1"/>
@@ -22,11 +22,10 @@
   </sheets>
   <externalReferences>
     <externalReference r:id="rId7"/>
-    <externalReference r:id="rId8"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">COMPTAB!$A$1:$Y$72</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Compte Banque'!$B$6:$R$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">COMPTAB!$A$1:$Y$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Compte Banque'!$B$6:$R$73</definedName>
     <definedName name="aaa" localSheetId="1">#REF!</definedName>
     <definedName name="aaa">#REF!</definedName>
     <definedName name="Anniversaire" localSheetId="1">#REF!,#REF!,#REF!,#REF!</definedName>
@@ -107,7 +106,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="57" r:id="rId9"/>
+    <pivotCache cacheId="23" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -124,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1343" uniqueCount="224">
   <si>
     <t>data</t>
   </si>
@@ -2271,34 +2270,7 @@
     <cellStyle name="Valore non valido" xfId="143" xr:uid="{00000000-0005-0000-0000-00008F000000}"/>
     <cellStyle name="Valore valido" xfId="144" xr:uid="{00000000-0005-0000-0000-000090000000}"/>
   </cellStyles>
-  <dxfs count="16">
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
+  <dxfs count="7">
     <dxf>
       <alignment horizontal="center"/>
     </dxf>
@@ -2374,43 +2346,17 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Compte Banque"/>
-      <sheetName val="COMPTAB"/>
-      <sheetName val="Pivot"/>
-      <sheetName val="Transfer"/>
-      <sheetName val="Frais anticipés"/>
-      <sheetName val="Participation Fee"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Edoardo" refreshedDate="46288.496283680557" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="67" xr:uid="{BEC7E0F4-8CE4-4ECA-8BD9-B963401BB7CD}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Edoardo" refreshedDate="46311.391143287037" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="68" xr:uid="{BEC7E0F4-8CE4-4ECA-8BD9-B963401BB7CD}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:Y68" sheet="COMPTAB"/>
+    <worksheetSource ref="A1:Y69" sheet="COMPTAB"/>
   </cacheSource>
   <cacheFields count="25">
     <cacheField name="data" numFmtId="14">
-      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2025-03-31T00:00:00" maxDate="2026-07-28T00:00:00"/>
+      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2025-03-31T00:00:00" maxDate="2026-10-16T00:00:00"/>
     </cacheField>
     <cacheField name="valuta " numFmtId="14">
-      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2025-08-29T00:00:00" maxDate="2026-07-28T00:00:00"/>
+      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2025-08-29T00:00:00" maxDate="2026-10-16T00:00:00"/>
     </cacheField>
     <cacheField name="Mese" numFmtId="1">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="12"/>
@@ -2560,7 +2506,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="67">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="68">
   <r>
     <d v="2025-08-29T00:00:00"/>
     <d v="2025-08-29T00:00:00"/>
@@ -4317,6 +4263,33 @@
     <m/>
   </r>
   <r>
+    <d v="2026-10-15T00:00:00"/>
+    <d v="2026-10-15T00:00:00"/>
+    <n v="10"/>
+    <x v="1"/>
+    <n v="2026"/>
+    <m/>
+    <m/>
+    <s v="LUX"/>
+    <n v="-250"/>
+    <m/>
+    <m/>
+    <n v="-250"/>
+    <n v="13971.967000000004"/>
+    <x v="1"/>
+    <x v="1"/>
+    <m/>
+    <x v="3"/>
+    <m/>
+    <x v="9"/>
+    <m/>
+    <x v="8"/>
+    <x v="0"/>
+    <s v="Green Enerbras One SCSp"/>
+    <x v="0"/>
+    <m/>
+  </r>
+  <r>
     <m/>
     <m/>
     <m/>
@@ -4374,7 +4347,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C83D047A-570D-470B-9382-988FF7984165}" name="PivotTable1" cacheId="57" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C83D047A-570D-470B-9382-988FF7984165}" name="PivotTable1" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A5:D60" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="3" colPageCount="1"/>
   <pivotFields count="25">
     <pivotField subtotalTop="0" showAll="0" defaultSubtotal="0"/>
@@ -4681,10 +4654,10 @@
     <dataField name="Sum of Importo" fld="11" baseField="1" baseItem="64" numFmtId="8"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="15">
+    <format dxfId="6">
       <pivotArea field="14" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="14">
+    <format dxfId="5">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="1">
@@ -4693,7 +4666,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="13">
+    <format dxfId="4">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -4999,7 +4972,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:U82"/>
+  <dimension ref="B1:U83"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.7109375" style="15" customWidth="1"/>
@@ -5298,7 +5271,7 @@
     </row>
     <row r="9" spans="2:21" s="25" customFormat="1" ht="15">
       <c r="B9" s="31">
-        <f t="shared" ref="B9:B68" si="0">B8+1</f>
+        <f t="shared" ref="B9:B69" si="0">B8+1</f>
         <v>3</v>
       </c>
       <c r="C9" s="32">
@@ -6485,7 +6458,7 @@
         <v>20000</v>
       </c>
       <c r="R29" s="35">
-        <f t="shared" ref="R29:R70" si="12">R28+Q29</f>
+        <f t="shared" ref="R29:R71" si="12">R28+Q29</f>
         <v>30241.517000000007</v>
       </c>
       <c r="U29" s="36"/>
@@ -8467,7 +8440,7 @@
         <v>197</v>
       </c>
       <c r="K64" s="172">
-        <f>-SUM(K78:K84)</f>
+        <f>-SUM(K79:K85)</f>
         <v>0</v>
       </c>
       <c r="L64" s="34" t="s">
@@ -8723,21 +8696,57 @@
       <c r="U68" s="36"/>
     </row>
     <row r="69" spans="2:21" s="25" customFormat="1" ht="15">
-      <c r="B69" s="31"/>
-      <c r="C69" s="32"/>
-      <c r="D69" s="32"/>
-      <c r="E69" s="32"/>
-      <c r="F69" s="32"/>
-      <c r="G69" s="32"/>
-      <c r="H69" s="32"/>
+      <c r="B69" s="31">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="C69" s="32">
+        <v>46310</v>
+      </c>
+      <c r="D69" s="32">
+        <v>46310</v>
+      </c>
+      <c r="E69" s="9">
+        <f t="shared" ref="E69" si="32">IF(C69="","",MONTH(C69))</f>
+        <v>10</v>
+      </c>
+      <c r="F69" s="9">
+        <f t="shared" ref="F69" si="33">IF(C69="","",YEAR(C69))</f>
+        <v>2026</v>
+      </c>
+      <c r="G69" s="9">
+        <v>2026</v>
+      </c>
+      <c r="H69" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="I69" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="J69" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="K69" s="25" t="s">
+        <v>51</v>
+      </c>
       <c r="L69" s="34"/>
+      <c r="M69" s="47" t="s">
+        <v>95</v>
+      </c>
       <c r="N69" s="58"/>
-      <c r="O69" s="27"/>
-      <c r="P69" s="27"/>
-      <c r="Q69" s="27"/>
+      <c r="O69" s="27">
+        <v>-250</v>
+      </c>
+      <c r="P69" s="27">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="27">
+        <f t="shared" ref="Q69" si="34">O69+P69</f>
+        <v>-250</v>
+      </c>
       <c r="R69" s="35">
         <f t="shared" si="12"/>
-        <v>14221.967000000004</v>
+        <v>13971.967000000004</v>
       </c>
       <c r="U69" s="36"/>
     </row>
@@ -8750,146 +8759,120 @@
       <c r="G70" s="32"/>
       <c r="H70" s="32"/>
       <c r="L70" s="34"/>
-      <c r="M70" s="47"/>
       <c r="N70" s="58"/>
       <c r="O70" s="27"/>
       <c r="P70" s="27"/>
       <c r="Q70" s="27"/>
       <c r="R70" s="35">
         <f t="shared" si="12"/>
-        <v>14221.967000000004</v>
+        <v>13971.967000000004</v>
       </c>
       <c r="U70" s="36"/>
     </row>
     <row r="71" spans="2:21" s="25" customFormat="1" ht="15">
       <c r="B71" s="31"/>
-      <c r="C71" s="24"/>
-      <c r="D71" s="24"/>
-      <c r="E71" s="24"/>
-      <c r="F71" s="24"/>
-      <c r="G71" s="24"/>
-      <c r="H71" s="24"/>
-      <c r="L71" s="24"/>
-      <c r="M71" s="24"/>
+      <c r="C71" s="32"/>
+      <c r="D71" s="32"/>
+      <c r="E71" s="32"/>
+      <c r="F71" s="32"/>
+      <c r="G71" s="32"/>
+      <c r="H71" s="32"/>
+      <c r="L71" s="34"/>
+      <c r="M71" s="47"/>
       <c r="N71" s="58"/>
       <c r="O71" s="27"/>
       <c r="P71" s="27"/>
       <c r="Q71" s="27"/>
-      <c r="R71" s="35" t="str">
-        <f t="shared" ref="R71" si="32">IF(Q71="",".",R70+Q71)</f>
+      <c r="R71" s="35">
+        <f t="shared" si="12"/>
+        <v>13971.967000000004</v>
+      </c>
+      <c r="U71" s="36"/>
+    </row>
+    <row r="72" spans="2:21" s="25" customFormat="1" ht="15">
+      <c r="B72" s="31"/>
+      <c r="C72" s="24"/>
+      <c r="D72" s="24"/>
+      <c r="E72" s="24"/>
+      <c r="F72" s="24"/>
+      <c r="G72" s="24"/>
+      <c r="H72" s="24"/>
+      <c r="L72" s="24"/>
+      <c r="M72" s="24"/>
+      <c r="N72" s="58"/>
+      <c r="O72" s="27"/>
+      <c r="P72" s="27"/>
+      <c r="Q72" s="27"/>
+      <c r="R72" s="35" t="str">
+        <f t="shared" ref="R72" si="35">IF(Q72="",".",R71+Q72)</f>
         <v>.</v>
       </c>
-      <c r="U71" s="36"/>
-    </row>
-    <row r="72" spans="2:21" s="25" customFormat="1" ht="15">
-      <c r="B72" s="37"/>
-      <c r="C72" s="39"/>
-      <c r="D72" s="39"/>
-      <c r="E72" s="39"/>
-      <c r="F72" s="39"/>
-      <c r="G72" s="39"/>
-      <c r="H72" s="39"/>
-      <c r="I72" s="38"/>
-      <c r="J72" s="38"/>
-      <c r="K72" s="38"/>
-      <c r="L72" s="39"/>
-      <c r="M72" s="48"/>
-      <c r="N72" s="60"/>
-      <c r="O72" s="40">
-        <f>SUM(O7:O71)</f>
-        <v>15027.660000000033</v>
-      </c>
-      <c r="P72" s="40">
-        <f>SUM(P7:P71)</f>
+      <c r="U72" s="36"/>
+    </row>
+    <row r="73" spans="2:21" s="25" customFormat="1" ht="15">
+      <c r="B73" s="37"/>
+      <c r="C73" s="39"/>
+      <c r="D73" s="39"/>
+      <c r="E73" s="39"/>
+      <c r="F73" s="39"/>
+      <c r="G73" s="39"/>
+      <c r="H73" s="39"/>
+      <c r="I73" s="38"/>
+      <c r="J73" s="38"/>
+      <c r="K73" s="38"/>
+      <c r="L73" s="39"/>
+      <c r="M73" s="48"/>
+      <c r="N73" s="60"/>
+      <c r="O73" s="40">
+        <f>SUM(O7:O72)</f>
+        <v>14777.660000000033</v>
+      </c>
+      <c r="P73" s="40">
+        <f>SUM(P7:P72)</f>
         <v>-805.69299999999998</v>
       </c>
-      <c r="Q72" s="40">
-        <f>SUM(Q7:Q71)</f>
-        <v>14221.967000000004</v>
-      </c>
-      <c r="R72" s="41">
-        <f>INDEX(R7:R71,COUNTIF(R7:R71,"&lt;&gt;."))</f>
-        <v>14221.967000000004</v>
-      </c>
-      <c r="U72" s="36"/>
-    </row>
-    <row r="73" spans="2:21" s="18" customFormat="1">
-      <c r="B73" s="14"/>
-      <c r="C73" s="14"/>
-      <c r="D73" s="14"/>
-      <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="14"/>
-      <c r="H73" s="14"/>
-      <c r="I73" s="15"/>
-      <c r="J73" s="15"/>
-      <c r="K73" s="15"/>
-      <c r="L73" s="14"/>
-      <c r="M73" s="14"/>
-      <c r="N73" s="61"/>
-      <c r="O73" s="14"/>
-      <c r="P73" s="14"/>
-      <c r="Q73" s="16"/>
-      <c r="R73" s="17"/>
-    </row>
-    <row r="74" spans="2:21" s="25" customFormat="1" ht="15">
-      <c r="B74" s="31">
-        <f>B83+1</f>
-        <v>1</v>
-      </c>
-      <c r="C74" s="32"/>
-      <c r="D74" s="32"/>
-      <c r="E74" s="9" t="str">
-        <f t="shared" ref="E74:E76" si="33">IF(C74="","",MONTH(C74))</f>
-        <v/>
-      </c>
-      <c r="F74" s="9" t="str">
-        <f t="shared" ref="F74:F76" si="34">IF(C74="","",YEAR(C74))</f>
-        <v/>
-      </c>
-      <c r="G74" s="9"/>
-      <c r="H74" s="32" t="s">
-        <v>124</v>
-      </c>
-      <c r="I74" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="K74" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="L74" s="34"/>
-      <c r="M74" s="47"/>
-      <c r="N74" s="58"/>
-      <c r="O74" s="27">
-        <v>0</v>
-      </c>
-      <c r="P74" s="27">
-        <f>O74*$P$5</f>
-        <v>0</v>
-      </c>
-      <c r="Q74" s="27">
-        <f t="shared" ref="Q74:Q76" si="35">O74+P74</f>
-        <v>0</v>
-      </c>
-      <c r="R74" s="35">
-        <f>R83+Q74</f>
-        <v>0</v>
-      </c>
-      <c r="U74" s="36"/>
+      <c r="Q73" s="40">
+        <f>SUM(Q7:Q72)</f>
+        <v>13971.967000000004</v>
+      </c>
+      <c r="R73" s="41">
+        <f>INDEX(R7:R72,COUNTIF(R7:R72,"&lt;&gt;."))</f>
+        <v>13971.967000000004</v>
+      </c>
+      <c r="U73" s="36"/>
+    </row>
+    <row r="74" spans="2:21" s="18" customFormat="1">
+      <c r="B74" s="14"/>
+      <c r="C74" s="14"/>
+      <c r="D74" s="14"/>
+      <c r="E74" s="14"/>
+      <c r="F74" s="14"/>
+      <c r="G74" s="14"/>
+      <c r="H74" s="14"/>
+      <c r="I74" s="15"/>
+      <c r="J74" s="15"/>
+      <c r="K74" s="15"/>
+      <c r="L74" s="14"/>
+      <c r="M74" s="14"/>
+      <c r="N74" s="61"/>
+      <c r="O74" s="14"/>
+      <c r="P74" s="14"/>
+      <c r="Q74" s="16"/>
+      <c r="R74" s="17"/>
     </row>
     <row r="75" spans="2:21" s="25" customFormat="1" ht="15">
       <c r="B75" s="31">
-        <f>B74+1</f>
-        <v>2</v>
+        <f>B84+1</f>
+        <v>1</v>
       </c>
       <c r="C75" s="32"/>
       <c r="D75" s="32"/>
       <c r="E75" s="9" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" ref="E75:E77" si="36">IF(C75="","",MONTH(C75))</f>
         <v/>
       </c>
       <c r="F75" s="9" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" ref="F75:F77" si="37">IF(C75="","",YEAR(C75))</f>
         <v/>
       </c>
       <c r="G75" s="9"/>
@@ -8899,30 +8882,25 @@
       <c r="I75" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="J75" s="25" t="s">
-        <v>194</v>
-      </c>
       <c r="K75" s="25" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="L75" s="34"/>
-      <c r="M75" s="47" t="s">
-        <v>51</v>
-      </c>
+      <c r="M75" s="47"/>
       <c r="N75" s="58"/>
       <c r="O75" s="27">
         <v>0</v>
       </c>
       <c r="P75" s="27">
-        <f t="shared" ref="P75:P76" si="36">O75*$P$5</f>
+        <f>O75*$P$5</f>
         <v>0</v>
       </c>
       <c r="Q75" s="27">
-        <f t="shared" si="35"/>
+        <f t="shared" ref="Q75:Q77" si="38">O75+P75</f>
         <v>0</v>
       </c>
       <c r="R75" s="35">
-        <f>R74+Q75</f>
+        <f>R84+Q75</f>
         <v>0</v>
       </c>
       <c r="U75" s="36"/>
@@ -8930,16 +8908,16 @@
     <row r="76" spans="2:21" s="25" customFormat="1" ht="15">
       <c r="B76" s="31">
         <f>B75+1</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C76" s="32"/>
       <c r="D76" s="32"/>
       <c r="E76" s="9" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="F76" s="9" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="G76" s="9"/>
@@ -8950,26 +8928,25 @@
         <v>57</v>
       </c>
       <c r="J76" s="25" t="s">
-        <v>83</v>
+        <v>194</v>
       </c>
       <c r="K76" s="25" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="L76" s="34"/>
       <c r="M76" s="47" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="N76" s="58"/>
       <c r="O76" s="27">
-        <f>-O75</f>
         <v>0</v>
       </c>
       <c r="P76" s="27">
-        <f t="shared" si="36"/>
+        <f t="shared" ref="P76:P77" si="39">O76*$P$5</f>
         <v>0</v>
       </c>
       <c r="Q76" s="27">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="R76" s="35">
@@ -8978,23 +8955,74 @@
       </c>
       <c r="U76" s="36"/>
     </row>
-    <row r="80" spans="2:21">
-      <c r="I80" s="15" t="s">
-        <v>125</v>
-      </c>
+    <row r="77" spans="2:21" s="25" customFormat="1" ht="15">
+      <c r="B77" s="31">
+        <f>B76+1</f>
+        <v>3</v>
+      </c>
+      <c r="C77" s="32"/>
+      <c r="D77" s="32"/>
+      <c r="E77" s="9" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="F77" s="9" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="G77" s="9"/>
+      <c r="H77" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="I77" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="J77" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="K77" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="L77" s="34"/>
+      <c r="M77" s="47" t="s">
+        <v>30</v>
+      </c>
+      <c r="N77" s="58"/>
+      <c r="O77" s="27">
+        <f>-O76</f>
+        <v>0</v>
+      </c>
+      <c r="P77" s="27">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="Q77" s="27">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="R77" s="35">
+        <f>R76+Q77</f>
+        <v>0</v>
+      </c>
+      <c r="U77" s="36"/>
     </row>
     <row r="81" spans="9:9">
       <c r="I81" s="15" t="s">
-        <v>181</v>
+        <v>125</v>
       </c>
     </row>
     <row r="82" spans="9:9">
       <c r="I82" s="15" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="83" spans="9:9">
+      <c r="I83" s="15" t="s">
         <v>182</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B6:R72" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="B6:R73" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="Q5:R5"/>
   </mergeCells>
@@ -9006,7 +9034,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8710E11A-A65F-4A00-847E-0D0A3B6D4E14}">
-  <dimension ref="A1:Y74"/>
+  <dimension ref="A1:Y75"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="10.7109375" style="6" bestFit="1" customWidth="1"/>
@@ -13248,11 +13276,11 @@
         <v>46230</v>
       </c>
       <c r="C66" s="7">
-        <f t="shared" ref="C66:C98" si="7">IF(B66="","",MONTH(B66))</f>
+        <f t="shared" ref="C66:C68" si="7">IF(B66="","",MONTH(B66))</f>
         <v>7</v>
       </c>
       <c r="D66" s="7">
-        <f t="shared" ref="D66:D98" si="8">IF(B66="","",YEAR(B66))</f>
+        <f t="shared" ref="D66:D68" si="8">IF(B66="","",YEAR(B66))</f>
         <v>2026</v>
       </c>
       <c r="E66" s="7">
@@ -13299,104 +13327,103 @@
         <v>88</v>
       </c>
     </row>
-    <row r="67" spans="1:25" ht="16.5" customHeight="1">
+    <row r="67" spans="1:25">
+      <c r="A67" s="6">
+        <v>46310</v>
+      </c>
+      <c r="B67" s="6">
+        <v>46310</v>
+      </c>
+      <c r="C67" s="7">
+        <f t="shared" si="7"/>
+        <v>10</v>
+      </c>
+      <c r="D67" s="7">
+        <f t="shared" si="8"/>
+        <v>2026</v>
+      </c>
+      <c r="E67" s="7">
+        <v>2026</v>
+      </c>
       <c r="F67" s="46"/>
-      <c r="L67" s="6"/>
-      <c r="M67" s="68"/>
-      <c r="N67" s="69"/>
-      <c r="O67" s="68"/>
-      <c r="P67" s="68"/>
-      <c r="Q67" s="68"/>
-      <c r="R67" s="70"/>
-    </row>
-    <row r="68" spans="1:25" ht="15.75" thickBot="1">
+      <c r="G67" s="23"/>
+      <c r="H67" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="I67" s="8">
+        <v>-250</v>
+      </c>
+      <c r="L67" s="8">
+        <f>I67</f>
+        <v>-250</v>
+      </c>
+      <c r="M67" s="8">
+        <f t="shared" ref="M67" si="9">M66+L67</f>
+        <v>13971.967000000004</v>
+      </c>
+      <c r="N67" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="O67" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>96</v>
+      </c>
+      <c r="S67" t="s">
+        <v>93</v>
+      </c>
+      <c r="U67" t="s">
+        <v>95</v>
+      </c>
+      <c r="V67" t="s">
+        <v>82</v>
+      </c>
+      <c r="W67" t="s">
+        <v>51</v>
+      </c>
+      <c r="X67" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="68" spans="1:25" ht="16.5" customHeight="1">
       <c r="F68" s="46"/>
-    </row>
-    <row r="69" spans="1:25" ht="16.5" thickBot="1">
-      <c r="F69" s="185">
-        <f>SUM(F2:F68)</f>
+      <c r="L68" s="6"/>
+      <c r="M68" s="68"/>
+      <c r="N68" s="69"/>
+      <c r="O68" s="68"/>
+      <c r="P68" s="68"/>
+      <c r="Q68" s="68"/>
+      <c r="R68" s="70"/>
+    </row>
+    <row r="69" spans="1:25" ht="15.75" thickBot="1">
+      <c r="F69" s="46"/>
+    </row>
+    <row r="70" spans="1:25" ht="16.5" thickBot="1">
+      <c r="F70" s="185">
+        <f>SUM(F2:F69)</f>
         <v>1443941</v>
       </c>
-      <c r="G69" s="186">
-        <f>F69/-I69</f>
+      <c r="G70" s="186">
+        <f>F70/-I70</f>
         <v>6.0164208333333331</v>
       </c>
-      <c r="H69" s="187"/>
-      <c r="I69" s="188">
+      <c r="H70" s="187"/>
+      <c r="I70" s="188">
         <f>I21+I27+I33+I54+I65</f>
         <v>-240000</v>
       </c>
-      <c r="L69" s="45">
-        <f>SUBTOTAL(9,L2:L68)</f>
-        <v>14221.967000000004</v>
-      </c>
-      <c r="M69"/>
-    </row>
-    <row r="70" spans="1:25">
-      <c r="F70" s="46"/>
+      <c r="L70" s="45">
+        <f>SUBTOTAL(9,L2:L69)</f>
+        <v>13971.967000000004</v>
+      </c>
+      <c r="M70"/>
     </row>
     <row r="71" spans="1:25">
       <c r="F71" s="46"/>
     </row>
     <row r="72" spans="1:25">
-      <c r="C72" s="7" t="str">
-        <f>IF(B70="","",MONTH(B70))</f>
-        <v/>
-      </c>
-      <c r="D72" s="7" t="str">
-        <f>IF(B70="","",YEAR(B70))</f>
-        <v/>
-      </c>
       <c r="F72" s="46"/>
-      <c r="G72" s="23"/>
-      <c r="H72" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="I72" s="8">
-        <v>0</v>
-      </c>
-      <c r="J72" s="21">
-        <v>0.17</v>
-      </c>
-      <c r="K72" s="8">
-        <f>I70*J70</f>
-        <v>0</v>
-      </c>
-      <c r="L72" s="8">
-        <f>I72+K72</f>
-        <v>0</v>
-      </c>
-      <c r="M72" s="8">
-        <f>M71+L72</f>
-        <v>0</v>
-      </c>
-      <c r="N72" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="O72" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q72" t="s">
-        <v>42</v>
-      </c>
-      <c r="S72" t="s">
-        <v>195</v>
-      </c>
-      <c r="T72" s="56" t="s">
-        <v>138</v>
-      </c>
-      <c r="U72" t="s">
-        <v>68</v>
-      </c>
-      <c r="W72" t="s">
-        <v>51</v>
-      </c>
-      <c r="X72" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="Y72" s="9" t="s">
-        <v>37</v>
-      </c>
     </row>
     <row r="73" spans="1:25">
       <c r="C73" s="7" t="str">
@@ -13440,13 +13467,13 @@
         <v>42</v>
       </c>
       <c r="S73" t="s">
-        <v>84</v>
+        <v>195</v>
+      </c>
+      <c r="T73" s="56" t="s">
+        <v>138</v>
       </c>
       <c r="U73" t="s">
-        <v>30</v>
-      </c>
-      <c r="V73" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="W73" t="s">
         <v>51</v>
@@ -13473,18 +13500,17 @@
         <v>41</v>
       </c>
       <c r="I74" s="8">
-        <f>-I71</f>
         <v>0</v>
       </c>
       <c r="J74" s="21">
         <v>0.17</v>
       </c>
       <c r="K74" s="8">
-        <f>-K71</f>
+        <f>I72*J72</f>
         <v>0</v>
       </c>
       <c r="L74" s="8">
-        <f>I72+K72</f>
+        <f>I74+K74</f>
         <v>0</v>
       </c>
       <c r="M74" s="8">
@@ -13519,8 +13545,69 @@
         <v>37</v>
       </c>
     </row>
+    <row r="75" spans="1:25">
+      <c r="C75" s="7" t="str">
+        <f>IF(B73="","",MONTH(B73))</f>
+        <v/>
+      </c>
+      <c r="D75" s="7" t="str">
+        <f>IF(B73="","",YEAR(B73))</f>
+        <v/>
+      </c>
+      <c r="F75" s="46"/>
+      <c r="G75" s="23"/>
+      <c r="H75" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="I75" s="8">
+        <f>-I72</f>
+        <v>0</v>
+      </c>
+      <c r="J75" s="21">
+        <v>0.17</v>
+      </c>
+      <c r="K75" s="8">
+        <f>-K72</f>
+        <v>0</v>
+      </c>
+      <c r="L75" s="8">
+        <f>I73+K73</f>
+        <v>0</v>
+      </c>
+      <c r="M75" s="8">
+        <f>M74+L75</f>
+        <v>0</v>
+      </c>
+      <c r="N75" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="O75" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>42</v>
+      </c>
+      <c r="S75" t="s">
+        <v>84</v>
+      </c>
+      <c r="U75" t="s">
+        <v>30</v>
+      </c>
+      <c r="V75" t="s">
+        <v>82</v>
+      </c>
+      <c r="W75" t="s">
+        <v>51</v>
+      </c>
+      <c r="X75" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="Y75" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y72" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:Y73" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -13896,10 +13983,10 @@
         <v>-277</v>
       </c>
       <c r="C38" s="8">
-        <v>-784</v>
+        <v>-1034</v>
       </c>
       <c r="D38" s="8">
-        <v>-1061</v>
+        <v>-1311</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -14124,10 +14211,10 @@
         <v>50223.517</v>
       </c>
       <c r="C60" s="8">
-        <v>-36001.550000000003</v>
+        <v>-36251.550000000003</v>
       </c>
       <c r="D60" s="8">
-        <v>14221.966999999999</v>
+        <v>13971.966999999999</v>
       </c>
     </row>
   </sheetData>
@@ -15128,7 +15215,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="L2:L46 L48">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
